--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>305</v>
+        <v>174</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>156</v>
+        <v>328</v>
       </c>
       <c r="D3">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>1</v>
-      </c>
-      <c r="G3">
-        <v>35</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D2">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D3">
         <v>90</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
